--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9844dadb8edb49e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R550c18fc37cc48ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R18deb017d53b4326"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R35ea3647f66441ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R9a629f39a05c424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R5fdaacd7c4b14474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rfa9d9ac2743b472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R009a097f3e4c48f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rac5d4edf3fcf40a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc6d86d248c5f4316"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -657,24 +657,24 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="67" t="str">
-        <x:v>Windows入口</x:v>
+        <x:v>申请预检表</x:v>
       </x:c>
       <x:c r="B5" s="67" t="str">
-        <x:v>Ruby</x:v>
+        <x:v>CSV</x:v>
       </x:c>
       <x:c r="C5" s="67" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D5" s="67" t="str">
-        <x:v>output/run_precheck.rb</x:v>
+        <x:v>output/results/request_precheck.csv</x:v>
       </x:c>
       <x:c r="E5" s="67" t="str">
-        <x:v>从空目录生成八份结果</x:v>
+        <x:v>十份申请的规则比较</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="68" t="str">
-        <x:v>申请预检表</x:v>
+        <x:v>容器归一表</x:v>
       </x:c>
       <x:c r="B6" s="68" t="str">
         <x:v>CSV</x:v>
@@ -683,15 +683,15 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="D6" s="68" t="str">
-        <x:v>output/results/request_precheck.csv</x:v>
+        <x:v>output/results/normalized_containers.csv</x:v>
       </x:c>
       <x:c r="E6" s="68" t="str">
-        <x:v>十份申请的离线规则比较</x:v>
+        <x:v>记录显式值和默认值来源</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="67" t="str">
-        <x:v>容器归一表</x:v>
+        <x:v>累计用量轨迹</x:v>
       </x:c>
       <x:c r="B7" s="67" t="str">
         <x:v>CSV</x:v>
@@ -700,32 +700,32 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="D7" s="67" t="str">
-        <x:v>output/results/normalized_containers.csv</x:v>
+        <x:v>output/results/quota_trajectory.csv</x:v>
       </x:c>
       <x:c r="E7" s="67" t="str">
-        <x:v>记录显式值和默认值来源</x:v>
+        <x:v>初始状态和十份申请</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="68" t="str">
-        <x:v>累计用量轨迹</x:v>
+        <x:v>预检摘要</x:v>
       </x:c>
       <x:c r="B8" s="68" t="str">
-        <x:v>CSV</x:v>
+        <x:v>JSON</x:v>
       </x:c>
       <x:c r="C8" s="68" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D8" s="68" t="str">
-        <x:v>output/results/quota_trajectory.csv</x:v>
+        <x:v>output/results/precheck_summary.json</x:v>
       </x:c>
       <x:c r="E8" s="68" t="str">
-        <x:v>初始状态和十份申请</x:v>
+        <x:v>记录申请结果和最终用量</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="67" t="str">
-        <x:v>预检摘要</x:v>
+        <x:v>最终用量</x:v>
       </x:c>
       <x:c r="B9" s="67" t="str">
         <x:v>JSON</x:v>
@@ -734,35 +734,62 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>output/results/precheck_summary.json</x:v>
+        <x:v>output/results/final_usage.json</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>明确没有联系API服务器</x:v>
+        <x:v>记录有效申请累计后的七项资源用量</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="71" t="str">
-        <x:v>结果检查</x:v>
+        <x:v>Namespace客户端对象</x:v>
       </x:c>
       <x:c r="B10" s="71" t="str">
-        <x:v>JSON</x:v>
+        <x:v>YAML</x:v>
       </x:c>
       <x:c r="C10" s="71" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D10" s="71" t="str">
-        <x:v>output/results/validation.json</x:v>
+        <x:v>output/results/kubectl_namespace_dry_run.yaml</x:v>
       </x:c>
       <x:c r="E10" s="71" t="str">
-        <x:v>独立复算与边界检查</x:v>
+        <x:v>记录kubectl客户端生成的Namespace对象</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="71" t="str"/>
-      <x:c r="B11" s="71" t="str"/>
-      <x:c r="C11" s="71" t="str"/>
-      <x:c r="D11" s="71" t="str"/>
-      <x:c r="E11" s="71" t="str"/>
+      <x:c r="A11" s="71" t="str">
+        <x:v>ResourceQuota客户端对象</x:v>
+      </x:c>
+      <x:c r="B11" s="71" t="str">
+        <x:v>YAML</x:v>
+      </x:c>
+      <x:c r="C11" s="71" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D11" s="71" t="str">
+        <x:v>output/results/kubectl_quota_dry_run.yaml</x:v>
+      </x:c>
+      <x:c r="E11" s="71" t="str">
+        <x:v>记录kubectl客户端生成的ResourceQuota对象</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>使用说明</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Markdown</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>output/README.md</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>说明交付物用途和平台值班接手事项</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -790,7 +817,7 @@
         <x:v>正确值</x:v>
       </x:c>
       <x:c r="D1" s="65" t="str">
-        <x:v>来源与验证</x:v>
+        <x:v>判定依据</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
@@ -818,60 +845,44 @@
         <x:v>WITHIN_POLICY或NEEDS_CHANGE</x:v>
       </x:c>
       <x:c r="D3" s="67" t="str">
-        <x:v>离线预检枚举</x:v>
+        <x:v>提交前预检枚举</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="68" t="str">
-        <x:v>precheck_summary.json</x:v>
-      </x:c>
-      <x:c r="B4" s="68" t="str">
-        <x:v>api_server_contacted</x:v>
-      </x:c>
-      <x:c r="C4" s="68" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="D4" s="68" t="str">
-        <x:v>运行边界</x:v>
-      </x:c>
+      <x:c r="A4" s="68"/>
+      <x:c r="B4" s="68"/>
+      <x:c r="C4" s="68"/>
+      <x:c r="D4" s="68"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="67" t="str">
-        <x:v>precheck_summary.json</x:v>
-      </x:c>
-      <x:c r="B5" s="67" t="str">
-        <x:v>workloads_created</x:v>
-      </x:c>
-      <x:c r="C5" s="67" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="D5" s="67" t="str">
-        <x:v>运行边界</x:v>
-      </x:c>
+      <x:c r="A5" s="67"/>
+      <x:c r="B5" s="67"/>
+      <x:c r="C5" s="67"/>
+      <x:c r="D5" s="67"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="68" t="str"/>
-      <x:c r="B6" s="68" t="str"/>
-      <x:c r="C6" s="68" t="str"/>
-      <x:c r="D6" s="68" t="str"/>
+      <x:c r="A6" s="68"/>
+      <x:c r="B6" s="68"/>
+      <x:c r="C6" s="68"/>
+      <x:c r="D6" s="68"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="67" t="str"/>
-      <x:c r="B7" s="67" t="str"/>
-      <x:c r="C7" s="67" t="str"/>
-      <x:c r="D7" s="67" t="str"/>
+      <x:c r="A7" s="67"/>
+      <x:c r="B7" s="67"/>
+      <x:c r="C7" s="67"/>
+      <x:c r="D7" s="67"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="68" t="str"/>
-      <x:c r="B8" s="68" t="str"/>
-      <x:c r="C8" s="68" t="str"/>
-      <x:c r="D8" s="68" t="str"/>
+      <x:c r="A8" s="68"/>
+      <x:c r="B8" s="68"/>
+      <x:c r="C8" s="68"/>
+      <x:c r="D8" s="68"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="67" t="str"/>
-      <x:c r="B9" s="67" t="str"/>
-      <x:c r="C9" s="67" t="str"/>
-      <x:c r="D9" s="67" t="str"/>
+      <x:c r="A9" s="67"/>
+      <x:c r="B9" s="67"/>
+      <x:c r="C9" s="67"/>
+      <x:c r="D9" s="67"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -938,7 +949,7 @@
         <x:v>exact_result_files</x:v>
       </x:c>
       <x:c r="C4" s="68" t="str">
-        <x:v>final_usage.json；kubectl_namespace_dry_run.yaml；kubectl_quota_dry_run.yaml；normalized_containers.csv；precheck_summary.json；quota_trajectory.csv；request_precheck.csv；validation.json</x:v>
+        <x:v>final_usage.json；kubectl_namespace_dry_run.yaml；kubectl_quota_dry_run.yaml；normalized_containers.csv；precheck_summary.json；quota_trajectory.csv；request_precheck.csv</x:v>
       </x:c>
       <x:c r="D4" s="68" t="str">
         <x:v>输入合同</x:v>
